--- a/data/asignaciones.xlsx
+++ b/data/asignaciones.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sodexo-my.sharepoint.com/personal/andres_benavidesrodriguez_sodexo_com/Documents/Documents/proyecto_catalogo/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="8_{DAF8DC20-10C9-457E-A148-B63786AC149F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC43E170-668D-4673-8BB2-D9EB0788E266}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="8_{DAF8DC20-10C9-457E-A148-B63786AC149F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1FF50DCB-AD51-48D4-BBF1-3B4F388A3DF0}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Supplier list" sheetId="1" r:id="rId1"/>
     <sheet name="Comments" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Supplier list'!$A$1:$D$317</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Supplier list'!$D$1:$D$330</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -66,9 +66,6 @@
     <t>ALPHA BAKING MISSOURI</t>
   </si>
   <si>
-    <t>Jaime Alvarez Aguirre</t>
-  </si>
-  <si>
     <t>ALPHA BAKING WISCONSIN</t>
   </si>
   <si>
@@ -1051,6 +1048,9 @@
   </si>
   <si>
     <t>Andres Benavides Rodriguez</t>
+  </si>
+  <si>
+    <t>Sofia Rodriguez</t>
   </si>
 </sst>
 </file>
@@ -1498,7 +1498,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1518,10 +1518,10 @@
         <v>3</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -1532,7 +1532,7 @@
         <v>4</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>5</v>
@@ -1546,7 +1546,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>7</v>
@@ -1560,10 +1560,10 @@
         <v>8</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -1571,13 +1571,13 @@
         <v>1000098</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -1585,13 +1585,13 @@
         <v>1000455</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -1599,13 +1599,13 @@
         <v>1000767</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -1613,10 +1613,10 @@
         <v>1000451</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>5</v>
@@ -1627,10 +1627,10 @@
         <v>1000930</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>7</v>
@@ -1641,10 +1641,10 @@
         <v>1000034</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>5</v>
@@ -1655,13 +1655,13 @@
         <v>1000064</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -1669,13 +1669,13 @@
         <v>1000763</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -1683,13 +1683,13 @@
         <v>1000575</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -1697,10 +1697,10 @@
         <v>1102761</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>5</v>
@@ -1711,10 +1711,10 @@
         <v>1000758</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>7</v>
@@ -1725,13 +1725,13 @@
         <v>1000407</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -1739,13 +1739,13 @@
         <v>1136811</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -1753,10 +1753,10 @@
         <v>1128301</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>7</v>
@@ -1767,13 +1767,13 @@
         <v>1001091</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -1781,10 +1781,10 @@
         <v>1123371</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>5</v>
@@ -1795,13 +1795,13 @@
         <v>1000447</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -1809,10 +1809,10 @@
         <v>1000446</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>5</v>
@@ -1823,10 +1823,10 @@
         <v>1000445</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>7</v>
@@ -1837,13 +1837,13 @@
         <v>1000443</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -1851,13 +1851,13 @@
         <v>1000444</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -1865,13 +1865,13 @@
         <v>1000442</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -1879,13 +1879,13 @@
         <v>1000441</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -1893,10 +1893,10 @@
         <v>1000440</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>5</v>
@@ -1907,10 +1907,10 @@
         <v>1000439</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>7</v>
@@ -1921,13 +1921,13 @@
         <v>1000438</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
@@ -1935,13 +1935,13 @@
         <v>1000436</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -1949,13 +1949,13 @@
         <v>1000435</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
@@ -1963,13 +1963,13 @@
         <v>1000434</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
@@ -1977,10 +1977,10 @@
         <v>1000431</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>5</v>
@@ -1991,10 +1991,10 @@
         <v>1000432</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>7</v>
@@ -2005,10 +2005,10 @@
         <v>1000433</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>5</v>
@@ -2019,13 +2019,13 @@
         <v>1116212</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
@@ -2033,13 +2033,13 @@
         <v>1123321</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
@@ -2047,13 +2047,13 @@
         <v>1133602</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
@@ -2061,10 +2061,10 @@
         <v>1127581</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>5</v>
@@ -2075,13 +2075,13 @@
         <v>1000393</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
@@ -2089,10 +2089,10 @@
         <v>1001196</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>7</v>
@@ -2103,13 +2103,13 @@
         <v>1127521</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -2117,13 +2117,13 @@
         <v>1139245</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -2131,10 +2131,10 @@
         <v>1146781</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>7</v>
@@ -2145,10 +2145,10 @@
         <v>1136801</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>5</v>
@@ -2159,13 +2159,13 @@
         <v>1000718</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
@@ -2173,13 +2173,13 @@
         <v>1145182</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
@@ -2187,10 +2187,10 @@
         <v>1146142</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>7</v>
@@ -2201,13 +2201,13 @@
         <v>1000449</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
@@ -2215,13 +2215,13 @@
         <v>1000424</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
@@ -2229,10 +2229,10 @@
         <v>1137217</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>7</v>
@@ -2243,13 +2243,13 @@
         <v>1000785</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
@@ -2257,13 +2257,13 @@
         <v>1116265</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
@@ -2271,13 +2271,13 @@
         <v>1127527</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
@@ -2285,13 +2285,13 @@
         <v>1101481</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
@@ -2299,13 +2299,13 @@
         <v>1123862</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
@@ -2313,13 +2313,13 @@
         <v>1136834</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
@@ -2327,10 +2327,10 @@
         <v>1000793</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>7</v>
@@ -2341,13 +2341,13 @@
         <v>1000849</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
@@ -2355,13 +2355,13 @@
         <v>1127545</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
@@ -2369,13 +2369,13 @@
         <v>1000453</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -2383,13 +2383,13 @@
         <v>1000405</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
@@ -2397,13 +2397,13 @@
         <v>1000419</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
@@ -2411,13 +2411,13 @@
         <v>1129161</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -2425,13 +2425,13 @@
         <v>1134581</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -2439,13 +2439,13 @@
         <v>1118001</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -2453,13 +2453,13 @@
         <v>1133301</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
@@ -2467,10 +2467,10 @@
         <v>1123070</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D70" s="4" t="s">
         <v>5</v>
@@ -2481,13 +2481,13 @@
         <v>1142001</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D71" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
@@ -2495,13 +2495,13 @@
         <v>1146121</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -2509,13 +2509,13 @@
         <v>1000366</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
@@ -2523,13 +2523,13 @@
         <v>1112381</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
@@ -2537,13 +2537,13 @@
         <v>1000362</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D75" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
@@ -2551,13 +2551,13 @@
         <v>1111701</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
@@ -2565,10 +2565,10 @@
         <v>1101922</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D77" s="4" t="s">
         <v>5</v>
@@ -2579,10 +2579,10 @@
         <v>1000360</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>7</v>
@@ -2593,10 +2593,10 @@
         <v>1001102</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>5</v>
@@ -2607,13 +2607,13 @@
         <v>1104761</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
@@ -2621,13 +2621,13 @@
         <v>1119561</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
@@ -2635,13 +2635,13 @@
         <v>1142568</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="39.6" x14ac:dyDescent="0.3">
@@ -2649,10 +2649,10 @@
         <v>1140169</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>5</v>
@@ -2663,10 +2663,10 @@
         <v>1140161</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D84" s="4" t="s">
         <v>7</v>
@@ -2677,13 +2677,13 @@
         <v>1140164</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D85" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
@@ -2691,10 +2691,10 @@
         <v>1000335</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D86" s="4" t="s">
         <v>7</v>
@@ -2705,10 +2705,10 @@
         <v>1146021</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D87" s="4" t="s">
         <v>5</v>
@@ -2719,13 +2719,13 @@
         <v>1123510</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D88" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D88" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
@@ -2733,13 +2733,13 @@
         <v>1107387</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
@@ -2747,13 +2747,13 @@
         <v>1107381</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
@@ -2761,13 +2761,13 @@
         <v>1107390</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D91" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D91" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
@@ -2775,13 +2775,13 @@
         <v>1000991</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
@@ -2789,13 +2789,13 @@
         <v>1122841</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
@@ -2803,13 +2803,13 @@
         <v>1000381</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
@@ -2817,13 +2817,13 @@
         <v>1122841</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -2831,10 +2831,10 @@
         <v>1132388</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D96" s="4" t="s">
         <v>7</v>
@@ -2845,13 +2845,13 @@
         <v>1127441</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D97" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D97" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -2859,10 +2859,10 @@
         <v>1113135</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D98" s="4" t="s">
         <v>7</v>
@@ -2873,10 +2873,10 @@
         <v>1135928</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D99" s="4" t="s">
         <v>7</v>
@@ -2887,13 +2887,13 @@
         <v>1145907</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D100" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D100" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -2901,13 +2901,13 @@
         <v>1145915</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D101" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D101" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -2915,10 +2915,10 @@
         <v>1145911</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D102" s="4" t="s">
         <v>7</v>
@@ -2929,10 +2929,10 @@
         <v>1145901</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D103" s="4" t="s">
         <v>7</v>
@@ -2943,13 +2943,13 @@
         <v>1000579</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
@@ -2957,13 +2957,13 @@
         <v>1001163</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
@@ -2971,13 +2971,13 @@
         <v>1000846</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D106" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D106" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -2985,10 +2985,10 @@
         <v>1001104</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D107" s="4" t="s">
         <v>5</v>
@@ -2999,10 +2999,10 @@
         <v>1116801</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D108" s="4" t="s">
         <v>7</v>
@@ -3013,13 +3013,13 @@
         <v>1000076</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
@@ -3027,13 +3027,13 @@
         <v>1001229</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D110" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D110" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
@@ -3041,13 +3041,13 @@
         <v>1102322</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
@@ -3055,10 +3055,10 @@
         <v>1000909</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D112" s="4" t="s">
         <v>5</v>
@@ -3069,10 +3069,10 @@
         <v>1000464</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D113" s="4" t="s">
         <v>7</v>
@@ -3083,10 +3083,10 @@
         <v>1000465</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D114" s="4" t="s">
         <v>7</v>
@@ -3097,13 +3097,13 @@
         <v>1000466</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
@@ -3111,13 +3111,13 @@
         <v>1000467</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D116" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D116" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
@@ -3125,13 +3125,13 @@
         <v>1000468</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
@@ -3139,10 +3139,10 @@
         <v>1000469</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D118" s="4" t="s">
         <v>5</v>
@@ -3153,10 +3153,10 @@
         <v>1000470</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D119" s="4" t="s">
         <v>7</v>
@@ -3167,13 +3167,13 @@
         <v>1000471</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
@@ -3181,13 +3181,13 @@
         <v>1000472</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
@@ -3195,13 +3195,13 @@
         <v>1000473</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D122" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D122" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
@@ -3209,13 +3209,13 @@
         <v>1000474</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
@@ -3223,10 +3223,10 @@
         <v>1000475</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D124" s="4" t="s">
         <v>5</v>
@@ -3237,10 +3237,10 @@
         <v>1000476</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D125" s="4" t="s">
         <v>7</v>
@@ -3251,13 +3251,13 @@
         <v>1000477</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
@@ -3265,13 +3265,13 @@
         <v>1111006</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
@@ -3279,13 +3279,13 @@
         <v>1101281</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D128" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D128" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
@@ -3293,13 +3293,13 @@
         <v>1001626</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
@@ -3307,13 +3307,13 @@
         <v>1102136</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
@@ -3321,13 +3321,13 @@
         <v>1123324</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -3335,13 +3335,13 @@
         <v>1107201</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.3">
@@ -3349,13 +3349,13 @@
         <v>1106821</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D133" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D133" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -3363,10 +3363,10 @@
         <v>1000862</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D134" s="4" t="s">
         <v>5</v>
@@ -3377,10 +3377,10 @@
         <v>1000953</v>
       </c>
       <c r="B135" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D135" s="4" t="s">
         <v>7</v>
@@ -3391,10 +3391,10 @@
         <v>1001089</v>
       </c>
       <c r="B136" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D136" s="4" t="s">
         <v>7</v>
@@ -3405,10 +3405,10 @@
         <v>1107904</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D137" s="4" t="s">
         <v>5</v>
@@ -3419,13 +3419,13 @@
         <v>1000942</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D138" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D138" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -3433,13 +3433,13 @@
         <v>1120394</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -3447,13 +3447,13 @@
         <v>1120387</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -3461,10 +3461,10 @@
         <v>1120398</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D141" s="4" t="s">
         <v>5</v>
@@ -3475,10 +3475,10 @@
         <v>1120384</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D142" s="4" t="s">
         <v>5</v>
@@ -3489,13 +3489,13 @@
         <v>1120381</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -3503,13 +3503,13 @@
         <v>1120390</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -3517,10 +3517,10 @@
         <v>1120401</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D145" s="4" t="s">
         <v>5</v>
@@ -3531,13 +3531,13 @@
         <v>1102084</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C146" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D146" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D146" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.3">
@@ -3545,13 +3545,13 @@
         <v>1000816</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C147" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D147" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D147" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.3">
@@ -3559,10 +3559,10 @@
         <v>1001185</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D148" s="4" t="s">
         <v>7</v>
@@ -3573,13 +3573,13 @@
         <v>1000877</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C149" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.3">
@@ -3587,13 +3587,13 @@
         <v>1000879</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="D150" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D150" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.3">
@@ -3601,10 +3601,10 @@
         <v>1106041</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D151" s="4" t="s">
         <v>5</v>
@@ -3615,13 +3615,13 @@
         <v>1125945</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -3629,13 +3629,13 @@
         <v>1130842</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="D153" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D153" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -3643,13 +3643,13 @@
         <v>1130861</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="D154" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D154" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.3">
@@ -3657,10 +3657,10 @@
         <v>1137559</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D155" s="4" t="s">
         <v>7</v>
@@ -3671,13 +3671,13 @@
         <v>1137537</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.3">
@@ -3685,13 +3685,13 @@
         <v>1147642</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.3">
@@ -3699,13 +3699,13 @@
         <v>1137203</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.3">
@@ -3713,10 +3713,10 @@
         <v>1137454</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D159" s="4" t="s">
         <v>7</v>
@@ -3727,10 +3727,10 @@
         <v>1136441</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D160" s="4" t="s">
         <v>7</v>
@@ -3741,10 +3741,10 @@
         <v>1136574</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D161" s="4" t="s">
         <v>7</v>
@@ -3755,13 +3755,13 @@
         <v>1137401</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C162" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.3">
@@ -3769,10 +3769,10 @@
         <v>1000269</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D163" s="4" t="s">
         <v>5</v>
@@ -3783,10 +3783,10 @@
         <v>1107841</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C164" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D164" s="4" t="s">
         <v>7</v>
@@ -3797,13 +3797,13 @@
         <v>1000267</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.3">
@@ -3811,13 +3811,13 @@
         <v>1000265</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.3">
@@ -3825,13 +3825,13 @@
         <v>1000261</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.3">
@@ -3839,13 +3839,13 @@
         <v>1000259</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="D168" s="4" t="s">
-        <v>9</v>
+        <v>309</v>
+      </c>
+      <c r="D168" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.3">
@@ -3853,13 +3853,13 @@
         <v>1000257</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.3">
@@ -3867,10 +3867,10 @@
         <v>1000062</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D170" s="4" t="s">
         <v>5</v>
@@ -3881,10 +3881,10 @@
         <v>1103541</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D171" s="4" t="s">
         <v>7</v>
@@ -3895,13 +3895,13 @@
         <v>1107424</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.3">
@@ -3909,13 +3909,13 @@
         <v>1104041</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="174" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -3923,13 +3923,13 @@
         <v>1111823</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="D174" s="4" t="s">
-        <v>9</v>
+        <v>309</v>
+      </c>
+      <c r="D174" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.3">
@@ -3937,13 +3937,13 @@
         <v>1000290</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.3">
@@ -3951,10 +3951,10 @@
         <v>1000291</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D176" s="4" t="s">
         <v>5</v>
@@ -3965,10 +3965,10 @@
         <v>1132481</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D177" s="4" t="s">
         <v>7</v>
@@ -3979,13 +3979,13 @@
         <v>1116076</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="D178" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D178" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.3">
@@ -3993,13 +3993,13 @@
         <v>1000288</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.3">
@@ -4007,13 +4007,13 @@
         <v>1001231</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.3">
@@ -4021,10 +4021,10 @@
         <v>1001205</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D181" s="4" t="s">
         <v>7</v>
@@ -4035,13 +4035,13 @@
         <v>1118971</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>310</v>
-      </c>
-      <c r="D182" s="4" t="s">
-        <v>9</v>
+        <v>309</v>
+      </c>
+      <c r="D182" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.3">
@@ -4049,13 +4049,13 @@
         <v>1107701</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.3">
@@ -4063,10 +4063,10 @@
         <v>1107895</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D184" s="4" t="s">
         <v>5</v>
@@ -4077,13 +4077,13 @@
         <v>1000295</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.3">
@@ -4091,10 +4091,10 @@
         <v>1000316</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D186" s="4" t="s">
         <v>5</v>
@@ -4105,10 +4105,10 @@
         <v>1000302</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D187" s="4" t="s">
         <v>7</v>
@@ -4119,10 +4119,10 @@
         <v>1000312</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D188" s="4" t="s">
         <v>7</v>
@@ -4133,13 +4133,13 @@
         <v>1000296</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D189" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="190" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -4147,13 +4147,13 @@
         <v>1000305</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>310</v>
-      </c>
-      <c r="D190" s="4" t="s">
-        <v>9</v>
+        <v>309</v>
+      </c>
+      <c r="D190" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="191" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -4161,13 +4161,13 @@
         <v>1000308</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D191" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.3">
@@ -4175,10 +4175,10 @@
         <v>1000304</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D192" s="4" t="s">
         <v>5</v>
@@ -4189,10 +4189,10 @@
         <v>1000300</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D193" s="4" t="s">
         <v>7</v>
@@ -4203,13 +4203,13 @@
         <v>1105082</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D194" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.3">
@@ -4217,13 +4217,13 @@
         <v>1000315</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D195" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="196" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -4231,13 +4231,13 @@
         <v>1000313</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="D196" s="4" t="s">
-        <v>9</v>
+        <v>309</v>
+      </c>
+      <c r="D196" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="197" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -4245,13 +4245,13 @@
         <v>1000303</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D197" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.3">
@@ -4259,10 +4259,10 @@
         <v>1000311</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D198" s="4" t="s">
         <v>5</v>
@@ -4273,10 +4273,10 @@
         <v>1000299</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D199" s="4" t="s">
         <v>7</v>
@@ -4287,13 +4287,13 @@
         <v>1000307</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D200" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.3">
@@ -4301,13 +4301,13 @@
         <v>1000659</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D201" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.3">
@@ -4315,13 +4315,13 @@
         <v>1104241</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="D202" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D202" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.3">
@@ -4329,13 +4329,13 @@
         <v>1001190</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D203" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.3">
@@ -4343,10 +4343,10 @@
         <v>1110962</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D204" s="4" t="s">
         <v>5</v>
@@ -4357,10 +4357,10 @@
         <v>1000240</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D205" s="4" t="s">
         <v>7</v>
@@ -4371,13 +4371,13 @@
         <v>1000235</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="D206" s="4" t="s">
-        <v>9</v>
+        <v>309</v>
+      </c>
+      <c r="D206" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.3">
@@ -4385,13 +4385,13 @@
         <v>1000233</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D207" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.3">
@@ -4399,13 +4399,13 @@
         <v>1000231</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="D208" s="4" t="s">
-        <v>9</v>
+        <v>309</v>
+      </c>
+      <c r="D208" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.3">
@@ -4413,13 +4413,13 @@
         <v>1108121</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C209" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D209" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.3">
@@ -4427,13 +4427,13 @@
         <v>1000647</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D210" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.3">
@@ -4441,10 +4441,10 @@
         <v>1000253</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C211" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D211" s="4" t="s">
         <v>7</v>
@@ -4455,10 +4455,10 @@
         <v>1116206</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D212" s="4" t="s">
         <v>5</v>
@@ -4469,13 +4469,13 @@
         <v>1000251</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D213" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.3">
@@ -4483,13 +4483,13 @@
         <v>1000944</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="D214" s="4" t="s">
-        <v>9</v>
+        <v>309</v>
+      </c>
+      <c r="D214" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.3">
@@ -4497,13 +4497,13 @@
         <v>1001244</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="D215" s="4" t="s">
-        <v>9</v>
+        <v>309</v>
+      </c>
+      <c r="D215" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="216" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -4511,13 +4511,13 @@
         <v>1000641</v>
       </c>
       <c r="B216" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D216" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.3">
@@ -4525,10 +4525,10 @@
         <v>1001180</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D217" s="4" t="s">
         <v>5</v>
@@ -4539,13 +4539,13 @@
         <v>1000246</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="D218" s="4" t="s">
-        <v>9</v>
+        <v>309</v>
+      </c>
+      <c r="D218" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.3">
@@ -4553,13 +4553,13 @@
         <v>1000244</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D219" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="220" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -4567,13 +4567,13 @@
         <v>1118198</v>
       </c>
       <c r="B220" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="D220" s="4" t="s">
-        <v>9</v>
+        <v>309</v>
+      </c>
+      <c r="D220" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.3">
@@ -4581,13 +4581,13 @@
         <v>1000820</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D221" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.3">
@@ -4595,10 +4595,10 @@
         <v>1102124</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C222" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D222" s="4" t="s">
         <v>5</v>
@@ -4609,10 +4609,10 @@
         <v>1118941</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D223" s="4" t="s">
         <v>5</v>
@@ -4623,10 +4623,10 @@
         <v>1107721</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C224" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D224" s="4" t="s">
         <v>7</v>
@@ -4637,10 +4637,10 @@
         <v>1125741</v>
       </c>
       <c r="B225" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C225" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D225" s="4" t="s">
         <v>5</v>
@@ -4651,13 +4651,13 @@
         <v>1001570</v>
       </c>
       <c r="B226" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C226" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D226" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="227" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -4665,13 +4665,13 @@
         <v>1123581</v>
       </c>
       <c r="B227" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="D227" s="4" t="s">
-        <v>9</v>
+        <v>309</v>
+      </c>
+      <c r="D227" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.3">
@@ -4679,13 +4679,13 @@
         <v>1000506</v>
       </c>
       <c r="B228" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D228" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="229" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -4693,10 +4693,10 @@
         <v>1000643</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D229" s="4" t="s">
         <v>5</v>
@@ -4707,10 +4707,10 @@
         <v>1000486</v>
       </c>
       <c r="B230" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C230" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D230" s="4" t="s">
         <v>7</v>
@@ -4721,10 +4721,10 @@
         <v>1118964</v>
       </c>
       <c r="B231" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D231" s="4" t="s">
         <v>7</v>
@@ -4735,13 +4735,13 @@
         <v>1118961</v>
       </c>
       <c r="B232" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D232" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.3">
@@ -4749,13 +4749,13 @@
         <v>1000484</v>
       </c>
       <c r="B233" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="D233" s="4" t="s">
-        <v>9</v>
+        <v>309</v>
+      </c>
+      <c r="D233" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="234" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -4763,10 +4763,10 @@
         <v>1123636</v>
       </c>
       <c r="B234" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C234" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D234" s="4" t="s">
         <v>7</v>
@@ -4777,10 +4777,10 @@
         <v>1107901</v>
       </c>
       <c r="B235" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C235" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D235" s="4" t="s">
         <v>7</v>
@@ -4791,13 +4791,13 @@
         <v>1107724</v>
       </c>
       <c r="B236" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C236" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D236" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="237" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -4805,13 +4805,13 @@
         <v>1129301</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C237" s="6" t="s">
-        <v>310</v>
-      </c>
-      <c r="D237" s="4" t="s">
-        <v>9</v>
+        <v>309</v>
+      </c>
+      <c r="D237" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.3">
@@ -4819,13 +4819,13 @@
         <v>1000255</v>
       </c>
       <c r="B238" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C238" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D238" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.3">
@@ -4833,10 +4833,10 @@
         <v>1137793</v>
       </c>
       <c r="B239" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C239" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D239" s="4" t="s">
         <v>5</v>
@@ -4847,10 +4847,10 @@
         <v>1137797</v>
       </c>
       <c r="B240" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C240" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D240" s="4" t="s">
         <v>7</v>
@@ -4861,13 +4861,13 @@
         <v>1134682</v>
       </c>
       <c r="B241" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C241" s="6" t="s">
-        <v>310</v>
-      </c>
-      <c r="D241" s="4" t="s">
-        <v>9</v>
+        <v>309</v>
+      </c>
+      <c r="D241" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.3">
@@ -4875,10 +4875,10 @@
         <v>1136106</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C242" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D242" s="4" t="s">
         <v>7</v>
@@ -4889,13 +4889,13 @@
         <v>1143282</v>
       </c>
       <c r="B243" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C243" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D243" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="244" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -4903,13 +4903,13 @@
         <v>1143464</v>
       </c>
       <c r="B244" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C244" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D244" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D244" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="245" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -4917,10 +4917,10 @@
         <v>1145681</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C245" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D245" s="4" t="s">
         <v>7</v>
@@ -4931,13 +4931,13 @@
         <v>1146801</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C246" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D246" s="8" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.3">
@@ -4945,10 +4945,10 @@
         <v>1001004</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C247" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D247" s="4" t="s">
         <v>5</v>
@@ -4959,10 +4959,10 @@
         <v>1111902</v>
       </c>
       <c r="B248" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C248" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D248" s="4" t="s">
         <v>7</v>
@@ -4973,10 +4973,10 @@
         <v>1000459</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C249" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D249" s="4" t="s">
         <v>5</v>
@@ -4987,13 +4987,13 @@
         <v>1000498</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C250" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D250" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.3">
@@ -5001,13 +5001,13 @@
         <v>1114281</v>
       </c>
       <c r="B251" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C251" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D251" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.3">
@@ -5015,10 +5015,10 @@
         <v>1001178</v>
       </c>
       <c r="B252" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C252" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D252" s="4" t="s">
         <v>5</v>
@@ -5029,10 +5029,10 @@
         <v>1000495</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C253" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D253" s="4" t="s">
         <v>7</v>
@@ -5043,10 +5043,10 @@
         <v>1000496</v>
       </c>
       <c r="B254" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C254" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D254" s="4" t="s">
         <v>7</v>
@@ -5057,13 +5057,13 @@
         <v>1107104</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C255" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D255" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.3">
@@ -5071,13 +5071,13 @@
         <v>1000712</v>
       </c>
       <c r="B256" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C256" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D256" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.3">
@@ -5085,13 +5085,13 @@
         <v>1000806</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C257" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D257" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D257" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.3">
@@ -5099,13 +5099,13 @@
         <v>1001200</v>
       </c>
       <c r="B258" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C258" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D258" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.3">
@@ -5113,13 +5113,13 @@
         <v>1105384</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C259" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D259" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D259" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.3">
@@ -5127,10 +5127,10 @@
         <v>1001063</v>
       </c>
       <c r="B260" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C260" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D260" s="4" t="s">
         <v>5</v>
@@ -5141,10 +5141,10 @@
         <v>1102139</v>
       </c>
       <c r="B261" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C261" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D261" s="4" t="s">
         <v>7</v>
@@ -5155,13 +5155,13 @@
         <v>1000494</v>
       </c>
       <c r="B262" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C262" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D262" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D262" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.3">
@@ -5169,13 +5169,13 @@
         <v>1116781</v>
       </c>
       <c r="B263" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C263" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D263" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.3">
@@ -5183,13 +5183,13 @@
         <v>1123202</v>
       </c>
       <c r="B264" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C264" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D264" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="265" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -5197,10 +5197,10 @@
         <v>1107861</v>
       </c>
       <c r="B265" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C265" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D265" s="4" t="s">
         <v>5</v>
@@ -5211,10 +5211,10 @@
         <v>1107881</v>
       </c>
       <c r="B266" s="5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C266" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D266" s="4" t="s">
         <v>7</v>
@@ -5225,13 +5225,13 @@
         <v>1107884</v>
       </c>
       <c r="B267" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C267" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D267" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="268" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -5239,13 +5239,13 @@
         <v>1107887</v>
       </c>
       <c r="B268" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C268" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D268" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.3">
@@ -5253,22 +5253,22 @@
         <v>1113567</v>
       </c>
       <c r="B269" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C269" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D269" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D269" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="270" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A270" s="7"/>
       <c r="B270" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C270" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D270" s="4" t="s">
         <v>5</v>
@@ -5279,10 +5279,10 @@
         <v>1107881</v>
       </c>
       <c r="B271" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C271" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D271" s="4" t="s">
         <v>7</v>
@@ -5293,13 +5293,13 @@
         <v>1123449</v>
       </c>
       <c r="B272" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C272" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D272" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.3">
@@ -5307,13 +5307,13 @@
         <v>1106865</v>
       </c>
       <c r="B273" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C273" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D273" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.3">
@@ -5321,13 +5321,13 @@
         <v>1102133</v>
       </c>
       <c r="B274" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C274" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D274" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D274" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.3">
@@ -5335,10 +5335,10 @@
         <v>1116388</v>
       </c>
       <c r="B275" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C275" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D275" s="4" t="s">
         <v>5</v>
@@ -5349,10 +5349,10 @@
         <v>1114514</v>
       </c>
       <c r="B276" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C276" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D276" s="4" t="s">
         <v>7</v>
@@ -5363,10 +5363,10 @@
         <v>1105384</v>
       </c>
       <c r="B277" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C277" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D277" s="4" t="s">
         <v>5</v>
@@ -5377,13 +5377,13 @@
         <v>1116847</v>
       </c>
       <c r="B278" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C278" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D278" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="279" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -5391,13 +5391,13 @@
         <v>1116861</v>
       </c>
       <c r="B279" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C279" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D279" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D279" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.3">
@@ -5405,13 +5405,13 @@
         <v>1117162</v>
       </c>
       <c r="B280" s="5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C280" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D280" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="281" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -5419,13 +5419,13 @@
         <v>1140565</v>
       </c>
       <c r="B281" s="5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C281" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D281" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D281" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="282" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -5433,10 +5433,10 @@
         <v>1117221</v>
       </c>
       <c r="B282" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C282" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D282" s="4" t="s">
         <v>5</v>
@@ -5447,13 +5447,13 @@
         <v>1117187</v>
       </c>
       <c r="B283" s="5" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C283" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D283" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="284" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -5461,10 +5461,10 @@
         <v>1117204</v>
       </c>
       <c r="B284" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C284" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D284" s="4" t="s">
         <v>7</v>
@@ -5475,13 +5475,13 @@
         <v>1000492</v>
       </c>
       <c r="B285" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C285" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D285" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.3">
@@ -5489,13 +5489,13 @@
         <v>1000491</v>
       </c>
       <c r="B286" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C286" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D286" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D286" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.3">
@@ -5503,13 +5503,13 @@
         <v>1000493</v>
       </c>
       <c r="B287" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C287" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D287" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.3">
@@ -5517,13 +5517,13 @@
         <v>1125881</v>
       </c>
       <c r="B288" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C288" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D288" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D288" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.3">
@@ -5531,10 +5531,10 @@
         <v>1132625</v>
       </c>
       <c r="B289" s="5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C289" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D289" s="4" t="s">
         <v>5</v>
@@ -5545,13 +5545,13 @@
         <v>1000857</v>
       </c>
       <c r="B290" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C290" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D290" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.3">
@@ -5559,10 +5559,10 @@
         <v>1117568</v>
       </c>
       <c r="B291" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C291" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D291" s="4" t="s">
         <v>5</v>
@@ -5573,13 +5573,13 @@
         <v>1132582</v>
       </c>
       <c r="B292" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C292" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D292" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.3">
@@ -5587,13 +5587,13 @@
         <v>1133983</v>
       </c>
       <c r="B293" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C293" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D293" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D293" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.3">
@@ -5601,13 +5601,13 @@
         <v>1133702</v>
       </c>
       <c r="B294" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C294" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D294" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.3">
@@ -5615,10 +5615,10 @@
         <v>1133986</v>
       </c>
       <c r="B295" s="5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C295" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D295" s="4" t="s">
         <v>7</v>
@@ -5629,10 +5629,10 @@
         <v>1133681</v>
       </c>
       <c r="B296" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C296" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D296" s="4" t="s">
         <v>5</v>
@@ -5643,13 +5643,13 @@
         <v>1133961</v>
       </c>
       <c r="B297" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C297" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D297" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.3">
@@ -5657,13 +5657,13 @@
         <v>1133941</v>
       </c>
       <c r="B298" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C298" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D298" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.3">
@@ -5671,13 +5671,13 @@
         <v>1129501</v>
       </c>
       <c r="B299" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C299" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D299" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.3">
@@ -5685,13 +5685,13 @@
         <v>1136522</v>
       </c>
       <c r="B300" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C300" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D300" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.3">
@@ -5699,10 +5699,10 @@
         <v>1136525</v>
       </c>
       <c r="B301" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C301" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D301" s="4" t="s">
         <v>7</v>
@@ -5713,13 +5713,13 @@
         <v>1117190</v>
       </c>
       <c r="B302" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C302" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D302" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.3">
@@ -5727,10 +5727,10 @@
         <v>1133964</v>
       </c>
       <c r="B303" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C303" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D303" s="4" t="s">
         <v>7</v>
@@ -5741,13 +5741,13 @@
         <v>1117184</v>
       </c>
       <c r="B304" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C304" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D304" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="305" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -5755,10 +5755,10 @@
         <v>1140565</v>
       </c>
       <c r="B305" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C305" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D305" s="4" t="s">
         <v>5</v>
@@ -5769,10 +5769,10 @@
         <v>1146903</v>
       </c>
       <c r="B306" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C306" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D306" s="4" t="s">
         <v>7</v>
@@ -5783,13 +5783,13 @@
         <v>1132637</v>
       </c>
       <c r="B307" s="5" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C307" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D307" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D307" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.3">
@@ -5797,13 +5797,13 @@
         <v>1124121</v>
       </c>
       <c r="B308" s="5" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C308" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D308" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D308" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.3">
@@ -5811,13 +5811,13 @@
         <v>1000116</v>
       </c>
       <c r="B309" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C309" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D309" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.3">
@@ -5825,10 +5825,10 @@
         <v>1000128</v>
       </c>
       <c r="B310" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C310" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D310" s="4" t="s">
         <v>5</v>
@@ -5839,13 +5839,13 @@
         <v>1000119</v>
       </c>
       <c r="B311" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C311" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D311" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.3">
@@ -5853,10 +5853,10 @@
         <v>1000110</v>
       </c>
       <c r="B312" s="5" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C312" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D312" s="4" t="s">
         <v>7</v>
@@ -5867,13 +5867,13 @@
         <v>1000123</v>
       </c>
       <c r="B313" s="5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C313" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D313" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D313" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.3">
@@ -5881,13 +5881,13 @@
         <v>1000115</v>
       </c>
       <c r="B314" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C314" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D314" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D314" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.3">
@@ -5895,13 +5895,13 @@
         <v>1105688</v>
       </c>
       <c r="B315" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C315" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D315" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.3">
@@ -5909,10 +5909,10 @@
         <v>1000118</v>
       </c>
       <c r="B316" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C316" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D316" s="4" t="s">
         <v>5</v>
@@ -5923,13 +5923,13 @@
         <v>1000129</v>
       </c>
       <c r="B317" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C317" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D317" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.3">
@@ -5937,10 +5937,10 @@
         <v>1000127</v>
       </c>
       <c r="B318" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D318" s="4" t="s">
         <v>7</v>
@@ -5951,13 +5951,13 @@
         <v>1000126</v>
       </c>
       <c r="B319" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D319" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.3">
@@ -5965,13 +5965,13 @@
         <v>1000125</v>
       </c>
       <c r="B320" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="D320" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D320" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.3">
@@ -5979,13 +5979,13 @@
         <v>1000114</v>
       </c>
       <c r="B321" s="5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D321" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.3">
@@ -5993,10 +5993,10 @@
         <v>1000112</v>
       </c>
       <c r="B322" s="5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D322" s="4" t="s">
         <v>5</v>
@@ -6007,13 +6007,13 @@
         <v>1130904</v>
       </c>
       <c r="B323" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D323" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.3">
@@ -6021,10 +6021,10 @@
         <v>1000113</v>
       </c>
       <c r="B324" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D324" s="4" t="s">
         <v>7</v>
@@ -6035,13 +6035,13 @@
         <v>1000122</v>
       </c>
       <c r="B325" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D325" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.3">
@@ -6049,13 +6049,13 @@
         <v>1000111</v>
       </c>
       <c r="B326" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="D326" s="4" t="s">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="D326" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.3">
@@ -6063,13 +6063,13 @@
         <v>1000121</v>
       </c>
       <c r="B327" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D327" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.3">
@@ -6077,10 +6077,10 @@
         <v>1000120</v>
       </c>
       <c r="B328" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C328" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D328" t="s">
         <v>5</v>
@@ -6091,13 +6091,13 @@
         <v>1000117</v>
       </c>
       <c r="B329" s="5" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C329" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D329" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.3">
@@ -6105,10 +6105,10 @@
         <v>1000124</v>
       </c>
       <c r="B330" s="5" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C330" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D330" t="s">
         <v>7</v>
